--- a/data/source-participacon-momoento4-planeacion-teritorial/participacion2026-19-08ubate.xlsx
+++ b/data/source-participacon-momoento4-planeacion-teritorial/participacion2026-19-08ubate.xlsx
@@ -27428,9 +27428,6 @@
       <c r="R456" t="str">
         <v>ADMINISTRACIÓN DE EMPRESAS 1994</v>
       </c>
-      <c r="S456" t="str">
-        <v>ADMINISTRACION DE EMPRESAS</v>
-      </c>
     </row>
     <row r="457">
       <c r="A457">

--- a/data/source-participacon-momoento4-planeacion-teritorial/participacion2026-19-08ubate.xlsx
+++ b/data/source-participacon-momoento4-planeacion-teritorial/participacion2026-19-08ubate.xlsx
@@ -676,7 +676,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H5">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I5" t="str">
         <v>08:00 - 22:00</v>
@@ -965,7 +965,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H10">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I10" t="str">
         <v>08:00 - 22:00</v>
@@ -1443,7 +1443,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H18">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I18" t="str">
         <v>08:00 - 22:00</v>
@@ -1567,7 +1567,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H20">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I20" t="str">
         <v>08:00 - 22:00</v>
@@ -2192,7 +2192,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H31">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I31" t="str">
         <v>08:00 - 22:00</v>
@@ -2434,7 +2434,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H35">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I35" t="str">
         <v>08:00 - 22:00</v>
@@ -2614,7 +2614,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H38">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I38" t="str">
         <v>08:00 - 22:00</v>
@@ -2679,7 +2679,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H39">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I39" t="str">
         <v>08:00 - 22:00</v>
@@ -3272,7 +3272,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H49">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I49" t="str">
         <v>08:00 - 22:00</v>
@@ -4744,7 +4744,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H74">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I74" t="str">
         <v>08:00 - 22:00</v>
@@ -5163,7 +5163,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H81">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I81" t="str">
         <v>08:00 - 22:00</v>
@@ -5337,7 +5337,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H84">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I84" t="str">
         <v>08:00 - 22:00</v>
@@ -5520,7 +5520,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H87">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I87" t="str">
         <v>08:00 - 22:00</v>
@@ -5585,7 +5585,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H88">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I88" t="str">
         <v>08:00 - 22:00</v>
@@ -5827,7 +5827,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H92">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I92" t="str">
         <v>08:00 - 22:00</v>
@@ -6001,7 +6001,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H95">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I95" t="str">
         <v>08:00 - 22:00</v>
@@ -6116,7 +6116,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H97">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I97" t="str">
         <v>08:00 - 22:00</v>
@@ -6709,7 +6709,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H107">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I107" t="str">
         <v>08:00 - 22:00</v>
@@ -7606,7 +7606,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H122">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I122" t="str">
         <v>08:00 - 22:00</v>
@@ -7671,7 +7671,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H123">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I123" t="str">
         <v>08:00 - 22:00</v>
@@ -7736,7 +7736,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H124">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I124" t="str">
         <v>08:00 - 22:00</v>
@@ -8096,7 +8096,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H130">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I130" t="str">
         <v>08:00 - 22:00</v>
@@ -8220,7 +8220,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H132">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I132" t="str">
         <v>08:00 - 22:00</v>
@@ -8403,7 +8403,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H135">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I135" t="str">
         <v>08:00 - 22:00</v>
@@ -8692,7 +8692,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H140">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I140" t="str">
         <v>08:00 - 22:00</v>
@@ -8993,7 +8993,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H145">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I145" t="str">
         <v>08:00 - 22:00</v>
@@ -9583,7 +9583,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H155">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I155" t="str">
         <v>08:00 - 22:00</v>
@@ -10757,7 +10757,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H175">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I175" t="str">
         <v>08:00 - 22:00</v>
@@ -12052,7 +12052,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H197">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I197" t="str">
         <v>08:00 - 22:00</v>
@@ -12223,7 +12223,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H200">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I200" t="str">
         <v>08:00 - 22:00</v>
@@ -12819,7 +12819,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H210">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I210" t="str">
         <v>08:00 - 22:00</v>
@@ -13061,7 +13061,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H214">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I214" t="str">
         <v>08:00 - 22:00</v>
@@ -13533,7 +13533,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H222">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I222" t="str">
         <v>08:00 - 22:00</v>
@@ -13657,7 +13657,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H224">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I224" t="str">
         <v>08:00 - 22:00</v>
@@ -13831,7 +13831,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H227">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I227" t="str">
         <v>08:00 - 22:00</v>
@@ -14421,7 +14421,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H237">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I237" t="str">
         <v>08:00 - 22:00</v>
@@ -14958,7 +14958,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H246">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I246" t="str">
         <v>08:00 - 22:00</v>
@@ -15023,7 +15023,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H247">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I247" t="str">
         <v>08:00 - 22:00</v>
@@ -15324,7 +15324,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H252">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I252" t="str">
         <v>08:00 - 22:00</v>
@@ -16784,7 +16784,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H277">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I277" t="str">
         <v>08:00 - 22:00</v>
@@ -16908,7 +16908,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H279">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I279" t="str">
         <v>08:00 - 22:00</v>
@@ -17433,7 +17433,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H288">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I288" t="str">
         <v>08:00 - 22:00</v>
@@ -17498,7 +17498,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H289">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I289" t="str">
         <v>08:00 - 22:00</v>
@@ -18035,7 +18035,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H298">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I298" t="str">
         <v>08:00 - 22:00</v>
@@ -18622,7 +18622,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H308">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I308" t="str">
         <v>08:00 - 22:00</v>
@@ -19743,7 +19743,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H327">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I327" t="str">
         <v>08:00 - 22:00</v>
@@ -19808,7 +19808,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H328">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I328" t="str">
         <v>08:00 - 22:00</v>
@@ -20460,7 +20460,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H339">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I339" t="str">
         <v>08:00 - 22:00</v>
@@ -20584,7 +20584,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H341">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I341" t="str">
         <v>08:00 - 22:00</v>
@@ -21413,7 +21413,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H355">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I355" t="str">
         <v>08:00 - 22:00</v>
@@ -21761,7 +21761,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H361">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I361" t="str">
         <v>08:00 - 22:00</v>
@@ -22236,7 +22236,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H369">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I369" t="str">
         <v>08:00 - 22:00</v>
@@ -22351,7 +22351,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H371">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I371" t="str">
         <v>08:00 - 22:00</v>
@@ -22767,7 +22767,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H378">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I378" t="str">
         <v>08:00 - 22:00</v>
@@ -23242,7 +23242,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H386">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I386" t="str">
         <v>08:00 - 22:00</v>
@@ -23307,7 +23307,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H387">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I387" t="str">
         <v>08:00 - 22:00</v>
@@ -23959,7 +23959,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H398">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I398" t="str">
         <v>08:00 - 22:00</v>
@@ -24850,7 +24850,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H413">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I413" t="str">
         <v>08:00 - 22:00</v>
@@ -24906,7 +24906,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H414">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I414" t="str">
         <v>08:00 - 22:00</v>
@@ -25192,7 +25192,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H419">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I419" t="str">
         <v>08:00 - 22:00</v>
@@ -25617,7 +25617,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H426">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I426" t="str">
         <v>08:00 - 22:00</v>
@@ -26263,7 +26263,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H437">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I437" t="str">
         <v>08:00 - 22:00</v>
@@ -26797,7 +26797,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H446">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I446" t="str">
         <v>08:00 - 22:00</v>
@@ -27154,7 +27154,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H452">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I452" t="str">
         <v>08:00 - 22:00</v>
@@ -27278,7 +27278,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H454">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I454" t="str">
         <v>08:00 - 22:00</v>
@@ -27334,7 +27334,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H455">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I455" t="str">
         <v>08:00 - 22:00</v>
@@ -28095,7 +28095,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H468">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I468" t="str">
         <v>08:00 - 22:00</v>
